--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -2,30 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8235" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Admin" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Students" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Attendance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Students" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Attendance" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="&quot;Google Sans Text&quot;"/>
-      <color rgb="FF1F1F1F"/>
     </font>
   </fonts>
   <fills count="2">
@@ -33,25 +31,29 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -124,7 +126,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -314,217 +316,41 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="7.25" customWidth="1" style="2" min="1" max="1"/>
-    <col width="23" customWidth="1" style="2" min="2" max="2"/>
-    <col width="30.88" customWidth="1" style="2" min="3" max="3"/>
-  </cols>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Roll No.</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Email Address</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Employee ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>OTP Receiver Email</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Shah Rukh Khan</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>king.khan@studio.in</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Deepika Padukone</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>deepika.p@vogue.in</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Prabhas Raju</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>rebelstar@tollywood.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Alia Bhatt</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>alia.b@dharma.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Ranbir Kapoor</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>ranbir.k@rkfilms.in</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Samantha Ruth Prabhu</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>sam.ruth@southstars.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Yash (Naveen Kumar)</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>rocky.bhai@kgf.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>1008</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Rashmika Mandanna</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>rashmika.m@nationalcrush.in</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>1009</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Allu Arjun</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>pushpa.raj@thaggdele.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>1010</v>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>Triptii Dimri</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>triptii.d@newwave.in</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>1011</v>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>Vijay Sethupathi</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>makkal.selvan@kollywood.in</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>1012</v>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Kiara Advani</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>kiara.a@bollystars.com</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>anyone@example.com</t>
         </is>
       </c>
     </row>
@@ -539,30 +365,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>OTP Receiver Email</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Roll No</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>EMP001</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>anyone@example.com</t>
+      <c r="A2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Student One</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>student101@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Student Two</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>student102@example.com</t>
         </is>
       </c>
     </row>
@@ -577,160 +426,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <cols>
+    <col width="12.140625" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Roll No</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>Email</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Employee ID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="n">
+      <c r="A2" t="n">
         <v>101</v>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Student One</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>student101@example.com</t>
+      <c r="C2" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PRESENT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DBMS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dr. XYZ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EMP001</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="n">
-        <v>102</v>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>Student Two</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>student102@example.com</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>Roll No</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>Professor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="n">
+      <c r="A3" t="n">
         <v>101</v>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Student One</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>14-Feb</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="C3" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ABSENT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dr. XYZ</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dr. XYZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Student One</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>15:42:51</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>PRESENT</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr"/>
-      <c r="G2" s="0" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="n">
-        <v>101</v>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>Student One</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>14-Feb</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>ABSENT</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr"/>
-      <c r="G3" s="0" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
